--- a/data/trans_camb/IQ2606_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26,34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,72</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19,82</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,89</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27,11</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,16</t>
+          <t>20,14</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 14,39</t>
+          <t>-8,99; 19,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 38,45</t>
+          <t>2,65; 43,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 19,07</t>
+          <t>-10,86; 14,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,02; 43,55</t>
+          <t>-19,12; 34,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 12,68</t>
+          <t>-7,16; 11,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 36,01</t>
+          <t>1,3; 33,75</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>49,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>34,62%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 25,1</t>
+          <t>-15,95; 40,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 66,17</t>
+          <t>8,33; 94,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 40,88</t>
+          <t>-16,56; 25,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 95,83</t>
+          <t>-28,96; 58,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 23,78</t>
+          <t>-11,25; 22,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 66,0</t>
+          <t>3,67; 62,74</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,68</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>13,26</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>25,17</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,23</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30,78</t>
+          <t>24,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,23</t>
+          <t>27,74</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 18,39</t>
+          <t>12,13; 22,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,07; 32,14</t>
+          <t>22,59; 36,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,07; 22,82</t>
+          <t>7,92; 18,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,84; 36,83</t>
+          <t>15,22; 31,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,45; 18,73</t>
+          <t>11,37; 18,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,27; 33,12</t>
+          <t>22,26; 32,77</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>22,46%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,18; 32,68</t>
+          <t>20,9; 42,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 56,25</t>
+          <t>39,03; 69,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 43,91</t>
+          <t>12,76; 33,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,1; 70,03</t>
+          <t>24,75; 55,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 33,79</t>
+          <t>19,48; 34,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,62; 60,18</t>
+          <t>38,4; 58,89</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15,08</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20,22</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>7,96</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>12,75</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15,08</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,95</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,4</t>
+          <t>16,48</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 15,94</t>
+          <t>7,78; 23,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 23,03</t>
+          <t>8,78; 29,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,13; 22,97</t>
+          <t>0,37; 16,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 28,69</t>
+          <t>0,34; 23,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 16,97</t>
+          <t>5,85; 17,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,01; 24,12</t>
+          <t>7,48; 23,16</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>11,36%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22,6%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 24,29</t>
+          <t>10,67; 39,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 35,05</t>
+          <t>12,7; 47,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,33; 37,16</t>
+          <t>0,56; 25,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,5; 45,99</t>
+          <t>0,69; 35,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,8; 26,0</t>
+          <t>8,12; 26,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,37; 36,82</t>
+          <t>11,04; 35,13</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,85</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28,14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>10,93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21,57</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15,85</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28,17</t>
+          <t>20,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,08</t>
+          <t>24,62</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,09</t>
+          <t>11,82; 19,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,66</t>
+          <t>22,08; 32,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,78; 20,09</t>
+          <t>6,59; 14,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22,59; 33,03</t>
+          <t>14,03; 26,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,43</t>
+          <t>10,88; 16,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,09; 28,9</t>
+          <t>20,37; 28,93</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>48,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>17,6%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,32; 25,11</t>
+          <t>19,83; 36,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,02; 44,05</t>
+          <t>37,73; 59,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,71; 36,73</t>
+          <t>10,25; 25,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38,08; 59,63</t>
+          <t>22,51; 44,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,09; 28,23</t>
+          <t>17,73; 28,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,63; 49,46</t>
+          <t>33,27; 49,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IQ2606_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -513,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
+          <t>Menores que el verano pasado emplearon crema solar con factor de protección de 50 o más, siempre o casi siempre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -591,467 +600,319 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>4,89</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>26,34</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,14</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>4.891964216467826</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>26.33949059635304</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.724553782936655</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>13.50484479073135</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2.919995489751404</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>20.13596681826882</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 19,05</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2,65; 43,52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,86; 14,74</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,12; 34,38</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 11,9</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,3; 33,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.986265324476062</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2.65391832980022</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.85638674198867</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.11929495890809</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-7.159412148650983</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.304828821057935</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>49,62%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,62%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.04513247870619</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>43.51735793134881</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.73643778225076</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>34.37501752764005</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.90383220930082</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>33.74514875706424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-15,95; 40,19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8,33; 94,32</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-16,56; 25,32</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-28,96; 58,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-11,25; 22,44</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,67; 62,74</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.09215816698043038</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.4962013345042104</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.02737452668347692</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.2143677615264428</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05019852435587252</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3461634869997568</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>17,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>30,68</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,26</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,32</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.1595146099939447</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.08327236644535313</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.1656231232566913</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.2895955617680967</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1124666074996223</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.0366830949145811</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12,13; 22,35</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>22,59; 36,57</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,92; 18,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15,22; 31,45</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 18,79</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,26; 32,77</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.401865506143227</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.943157860209578</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.2532241246682385</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.5843621592947719</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.2243832685578565</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6273738767173838</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>55,59%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,65%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>17.2289251334375</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>30.67697750266909</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>13.25569091362553</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>24.22035463866305</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>15.32012275290309</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>27.74449271983189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>20,9; 42,8</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>39,03; 69,16</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12,76; 33,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24,75; 55,6</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19,48; 34,36</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,4; 58,89</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>12.1271402370372</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>22.58718480583757</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>7.915846654899615</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>15.22100792498211</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>11.37284681296565</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>22.26126921610971</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>15,08</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>20,22</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,72</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,61</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,48</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>22.34911265888219</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>36.56695478171689</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.69826200488544</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>31.44876117405876</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>18.79009194023609</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>32.77148981285562</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7,78; 23,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8,78; 29,51</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 16,25</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 23,24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,85; 17,57</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 23,16</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.3122242127278576</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5559310912003506</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.2245874550376511</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.410358678687608</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2686543668816471</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.4865286816769447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>22,6%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.2090030274352897</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.3902678165561912</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.1275888406967716</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>0.2474689745203067</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.1948196865113618</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.3840025604390982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>10,67; 39,63</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12,7; 47,03</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 25,32</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,69; 35,83</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>8,12; 26,86</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>11,04; 35,13</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.4280282547825651</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.6915782712786219</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3300005437317222</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.5560297662244343</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3436079359096881</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.5888599632069965</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +920,317 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>15,85</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>28,14</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,93</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,45</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,62</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>15.07671973036706</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>20.22493281074773</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7.963421896007949</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>12.72024277310351</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>11.60772077430206</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>16.47618199620723</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>11,82; 19,98</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>22,08; 32,92</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 14,91</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14,03; 26,44</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10,88; 16,22</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,37; 28,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>7.784186755171898</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>8.778541762424991</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.3722329171980655</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.3407105032917757</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5.852608173353429</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>7.483602238163062</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>48,91%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17,6%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>33,2%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,51%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>41,19%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>23.72298718317839</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>29.51298821278929</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>16.24992528055556</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>23.23967582836642</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>17.57266823488493</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>23.15708854795834</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>19,83; 36,44</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37,73; 59,14</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10,25; 25,34</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>22,51; 44,71</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17,73; 28,0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>33,27; 49,73</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.226010776109682</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3031861600581719</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.113578671677308</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1814230485899815</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.1697190336257049</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.2409018739000176</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.1066966175892113</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.1269635695956502</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.005560758480336075</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.006874323106040272</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.08124005605438545</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.1103968954492943</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.3963231384494075</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.4703221967906241</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.2531654572812521</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.3583046693709121</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2685814104491443</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.3513307856859384</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>15.85194768733559</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>28.13805060928594</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>10.93147369958692</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>20.62364671511804</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>13.45367566804146</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>24.6198506590824</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>11.82266264428779</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>22.0809420979475</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>6.591181147411358</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>14.027734436196</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>10.8751344518892</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>20.37329716121232</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>19.97918842083376</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>32.91613797314817</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>14.90701007347275</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>26.43869710886049</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>16.22361522931028</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>28.9278003082916</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.2755300546898927</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.4890805077181423</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1759793843603656</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.3320079937922087</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.225097084635533</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.4119213770468734</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.1982606562749643</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.377274265754399</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.1024562793505507</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0.2251299049793691</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.1773009413518783</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.3326819717646046</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.3643800480128059</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.5914324393292488</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.2533909061174189</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.4471292067541079</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.2800343904024828</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.4973324420879842</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1238,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
